--- a/Result/profitability/3090.xlsx
+++ b/Result/profitability/3090.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.27</v>
       </c>
       <c r="M2" t="n">
-        <v>1.25</v>
+        <v>1.49625</v>
       </c>
       <c r="N2" t="n">
-        <v>16.52125</v>
+        <v>16.7075</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,16 +780,16 @@
         <v>0.58</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1675</v>
+        <v>1.445</v>
       </c>
       <c r="N3" t="n">
-        <v>16.345</v>
+        <v>16.92125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.97</v>
       </c>
       <c r="M4" t="n">
-        <v>1.165</v>
+        <v>1.3575</v>
       </c>
       <c r="N4" t="n">
-        <v>16.76375</v>
+        <v>16.83125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.63</v>
       </c>
       <c r="M5" t="n">
-        <v>1.035</v>
+        <v>1.36625</v>
       </c>
       <c r="N5" t="n">
-        <v>16.76875</v>
+        <v>17.22</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.41</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01625</v>
+        <v>1.17125</v>
       </c>
       <c r="N6" t="n">
-        <v>16.905</v>
+        <v>17.17</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.47</v>
       </c>
       <c r="M7" t="n">
-        <v>0.82875</v>
+        <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>16.88625</v>
+        <v>16.90625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.35</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7975</v>
+        <v>0.9862500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>16.61125</v>
+        <v>16.39125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3090</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5154</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4221</v>
+      </c>
+      <c r="E75" t="n">
+        <v>932</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18.09</v>
+      </c>
+      <c r="G75" t="n">
+        <v>571</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.07%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>465</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1036</v>
+      </c>
+      <c r="K75" t="n">
+        <v>909</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.6175</v>
+      </c>
+      <c r="N75" t="n">
+        <v>16.74375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.888235294117647</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.760000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.08866498740554163</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>4.732142857142857</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.609999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2493093922651932</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
